--- a/artfynd/A 7652-2021 artfynd.xlsx
+++ b/artfynd/A 7652-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125429823</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>58001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 7652-2021 artfynd.xlsx
+++ b/artfynd/A 7652-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125429823</v>
       </c>
       <c r="B2" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7652-2021 artfynd.xlsx
+++ b/artfynd/A 7652-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125429823</v>
       </c>
       <c r="B2" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 7652-2021 artfynd.xlsx
+++ b/artfynd/A 7652-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,125 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128831104</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57022</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>sträckande NO</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Liden Upplo, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>364146</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6441204</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Magra</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Göran Frantz</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Göran Frantz</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7652-2021 artfynd.xlsx
+++ b/artfynd/A 7652-2021 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>128831104</v>
       </c>
       <c r="B3" t="n">
-        <v>57028</v>
+        <v>57030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 7652-2021 artfynd.xlsx
+++ b/artfynd/A 7652-2021 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>128831104</v>
       </c>
       <c r="B3" t="n">
-        <v>57030</v>
+        <v>57032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
